--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2022_los_lagos.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2022_los_lagos.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:39</t>
+    <t xml:space="preserve">2026-09-24 01:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -567,13 +567,13 @@
         <v>30</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.42</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="3">
@@ -590,13 +590,13 @@
         <v>30</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.61</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="4">
@@ -613,13 +613,13 @@
         <v>30</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.37</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="5">
@@ -636,13 +636,13 @@
         <v>30</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="6">
@@ -659,13 +659,13 @@
         <v>30</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="7">
@@ -685,7 +685,7 @@
         <v>0.16</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>-0.36</v>
@@ -708,7 +708,7 @@
         <v>-0.14</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0.18</v>
@@ -731,7 +731,7 @@
         <v>-0.13</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0.16</v>
@@ -754,7 +754,7 @@
         <v>0.04</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>-0.25</v>
@@ -777,7 +777,7 @@
         <v>0.03</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>-0.24</v>
@@ -800,7 +800,7 @@
         <v>0.25</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>-0.3</v>
@@ -823,7 +823,7 @@
         <v>0.2</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>-0.05</v>
@@ -843,13 +843,13 @@
         <v>30</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="15">
@@ -866,13 +866,13 @@
         <v>30</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="16">
@@ -892,7 +892,7 @@
         <v>-0.12</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>-0.07</v>
@@ -915,7 +915,7 @@
         <v>-0.35</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0.02</v>
@@ -938,7 +938,7 @@
         <v>-0.75</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>-0.02</v>
@@ -961,7 +961,7 @@
         <v>-0.4</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>-0.01</v>
@@ -984,7 +984,7 @@
         <v>-0.4</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>-0.06</v>
@@ -998,19 +998,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.02</v>
+        <v>-0.11</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.28</v>
+        <v>0.11</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="22">
@@ -1021,16 +1021,16 @@
         <v>31</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.25</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0.5</v>
@@ -1044,19 +1044,19 @@
         <v>31</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-0.44</v>
+        <v>-0.4</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.63</v>
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2022_los_lagos.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2022_los_lagos.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:29</t>
+    <t xml:space="preserve">2026-10-01 23:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2022_los_lagos.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2022_los_lagos.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:14</t>
+    <t xml:space="preserve">2026-10-05 19:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
